--- a/www/download/COUNTRY.BEL.zdW13.xlsx
+++ b/www/download/COUNTRY.BEL.zdW13.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Bélgica</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.7299483476926</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.767200650712243</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.885559181066731</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.89852905874464</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.938262384526172</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.08271977599631</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1165698681726</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.05752964628676</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.884017016719317</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.803923186934283</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.803793926163139</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.796431999331189</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.729660720440948</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.679902075880751</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.71694868628827</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3.867</t>
+          <t>-0.39511289587557</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3.878</t>
+          <t>-0.406318317075017</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3.904</t>
+          <t>-0.373707475424568</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>3.973</t>
+          <t>-0.366621506752562</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>4.028</t>
+          <t>-0.422351413925135</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4.109</t>
+          <t>-0.43251086785983</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.165</t>
+          <t>-0.464364246238836</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4.159</t>
+          <t>-0.500183516055804</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>4.16</t>
+          <t>-0.564779004543441</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>4.199</t>
+          <t>-0.613293223587781</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>4.258</t>
+          <t>-0.607923466948342</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>4.308</t>
+          <t>-0.603884212202214</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>4.378</t>
+          <t>-0.58126525555079</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>-0.526411777454433</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>4.438</t>
+          <t>-0.551979183828285</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3.169</t>
+          <t>-0.0421346549556707</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3.173</t>
+          <t>-0.0665928306037979</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3.198</t>
+          <t>-0.0208982490236137</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>3.268</t>
+          <t>-0.0147044107913741</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>3.323</t>
+          <t>-0.0958170694386415</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3.407</t>
+          <t>-0.12445429792704</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>-0.176012476084763</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>-0.238811299818695</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>3.472</t>
+          <t>-0.359781442308209</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>3.507</t>
+          <t>-0.406401755715968</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>3.563</t>
+          <t>-0.393682411528769</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>3.609</t>
+          <t>-0.383100884802501</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>3.672</t>
+          <t>-0.358183829199079</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>3.738</t>
+          <t>-0.287953334365282</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>3.717</t>
+          <t>-0.328991774283665</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>5537.162</t>
+          <t>0.0406046677140492</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>5534.511</t>
+          <t>0.0169090584272724</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>5603.697</t>
+          <t>0.0682219958710821</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>5685.502</t>
+          <t>0.0772454436289973</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>5787.52</t>
+          <t>-0.0251363077155414</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5961.599</t>
+          <t>-0.0343896566208736</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>6030.447</t>
+          <t>-0.090112698875097</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>5990.895</t>
+          <t>-0.164974109726454</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>5992.714</t>
+          <t>-0.401670527449917</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>6057.565</t>
+          <t>-0.34410727941458</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>6122.792</t>
+          <t>-0.328153256106741</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>6209.157</t>
+          <t>-0.31643358568357</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>6331.202</t>
+          <t>-0.25270835160328</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>6412.834</t>
+          <t>-0.180726946576867</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>6293.109</t>
+          <t>-0.229711015328372</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>4595.1</t>
+          <t>9561277790.70018</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>4585.6</t>
+          <t>8967786461.44638</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>4644.6</t>
+          <t>8615053792.51127</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>4729.2</t>
+          <t>8743942759.39498</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>4818.4</t>
+          <t>8817830762.80937</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>4982.1</t>
+          <t>9589279577.18918</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5057.8</t>
+          <t>9527632144.6464</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>5033.1</t>
+          <t>9222237189.66084</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>5028.4</t>
+          <t>9906251051.95125</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>5082.2</t>
+          <t>10449898401.1063</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>5144</t>
+          <t>10002168010.6904</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>5218.2</t>
+          <t>10811616938.52</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>5322.6</t>
+          <t>11385208650.8527</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>5400.1</t>
+          <t>13566541133.8166</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>5284.4</t>
+          <t>10051414222.5481</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>16.58</t>
+          <t>5041832495.58354</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>16.97</t>
+          <t>5171234670.17636</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>17.29</t>
+          <t>5001633711.3948</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>17.51</t>
+          <t>5066976461.20708</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>5667328203.47803</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>17.84</t>
+          <t>6013843045.83087</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>6499238072.30633</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>18.01</t>
+          <t>7009899623.97326</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>16.66</t>
+          <t>8610635499.64746</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>19.17</t>
+          <t>9149005829.20912</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>19.54</t>
+          <t>9088577584.60769</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>9100422235.47265</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>20.37</t>
+          <t>8808875999.74884</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>8153070635.15717</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>22.52</t>
+          <t>8502035301.22385</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>44.55</t>
+          <t>689127.342842912</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>45.79</t>
+          <t>679862.3486297</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>46.74</t>
+          <t>726670.584652277</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>47.59</t>
+          <t>725475.546010919</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>48.06</t>
+          <t>760306.29489221</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>49.98</t>
+          <t>830151.502029178</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>51.12</t>
+          <t>814806.665790319</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>51.96</t>
+          <t>767330.846601829</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>50.25</t>
+          <t>686756.472145855</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>54.52</t>
+          <t>629035.038350095</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>55.45</t>
+          <t>597012.009445448</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>56.16</t>
+          <t>572414.436728041</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>57.34</t>
+          <t>517641.103883208</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>527865.895553514</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>56.94</t>
+          <t>485544.550257112</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>38.86</t>
+          <t>22789.5683074509</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>37.24</t>
+          <t>22662.5939982593</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>35.97</t>
+          <t>22684.4085747658</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>34.9</t>
+          <t>22606.9210175435</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>23740.7586789752</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>32.18</t>
+          <t>24658.5860825102</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>30.88</t>
+          <t>24044.4762835432</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>30.02</t>
+          <t>24100.5982202833</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>33.09</t>
+          <t>25661.4172636123</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>26.31</t>
+          <t>28224.4111718515</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>25.01</t>
+          <t>29938.7846729403</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>24.04</t>
+          <t>31577.2777754955</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>22.29</t>
+          <t>35984.3946261532</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>21.15</t>
+          <t>39624.5098825539</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>20.54</t>
+          <t>36154.0248277153</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>11.57</t>
+          <t>82384.4496912924</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>11.92</t>
+          <t>77823.7357671771</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>12.22</t>
+          <t>74522.8142495611</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>12.43</t>
+          <t>74874.7296015944</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>12.57</t>
+          <t>78540.2111286253</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>12.73</t>
+          <t>86823.8823786023</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>12.97</t>
+          <t>83779.5355417079</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>13.13</t>
+          <t>82864.2935625629</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>13.27</t>
+          <t>95422.2401980469</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>13.94</t>
+          <t>110716.105309894</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>113502.675697585</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>14.25</t>
+          <t>128081.827910204</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>14.86</t>
+          <t>151971.246036199</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>17.05</t>
+          <t>198257.945460238</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>17.23</t>
+          <t>136929.996118079</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>45.83</t>
+          <t>-0.0886051839236751</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>47.21</t>
+          <t>-0.113248519459742</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>48.28</t>
+          <t>-0.0713834182981848</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>49.22</t>
+          <t>-0.0666623308383421</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>49.99</t>
+          <t>-0.149793372290852</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>51.71</t>
+          <t>-0.171561352361221</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>52.96</t>
+          <t>-0.221785701072929</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>53.85</t>
+          <t>-0.282001131259109</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>54.66</t>
+          <t>-0.416024519885219</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>56.73</t>
+          <t>-0.44450795038576</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>57.85</t>
+          <t>-0.434014844224709</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>58.73</t>
+          <t>-0.426598034137371</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>59.38</t>
+          <t>-0.395768540713735</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>58.74</t>
+          <t>-0.337660589285953</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>59.27</t>
+          <t>-0.378454709634137</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>40.87</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>38.35</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>37.44</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>35.56</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>34.07</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>33.03</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>32.07</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>29.34</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>27.95</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>27.02</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>25.76</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.7299483476926</t>
+          <t>1591.02448579787</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.767200650712243</t>
+          <t>1629.67001551957</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.885559181066731</t>
+          <t>1563.75722888767</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.89852905874464</t>
+          <t>1550.57871134807</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.938262384526172</t>
+          <t>1705.7041328434</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.08271977599631</t>
+          <t>1765.09403049544</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.1165698681726</t>
+          <t>1873.18764343997</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.05752964628676</t>
+          <t>2020.20627839915</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.884017016719317</t>
+          <t>2480.28606148912</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.803923186934283</t>
+          <t>2608.74095301792</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.803793926163139</t>
+          <t>2550.52530652001</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.796431999331189</t>
+          <t>2521.27671403473</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.729660720440948</t>
+          <t>2398.66028206203</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.679902075880751</t>
+          <t>2180.93516854076</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.71694868628827</t>
+          <t>2287.40691170244</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.146</t>
+          <t>8866526492.86958</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.141</t>
+          <t>8787971641.11707</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>8146657647.34527</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>8243823377.53306</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.131</t>
+          <t>8954544190.74166</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>9100515066.25698</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>9523984009.48354</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>10595492967.1785</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.162</t>
+          <t>12670862499.4509</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.183</t>
+          <t>13675287975.9802</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>13370337082.8317</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>13445757295.3513</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>13294891890.465</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>12351482545.1957</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.249</t>
+          <t>12131809575.8973</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>7977444025.06141</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.167</t>
+          <t>7700746791.53971</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>7170841734.19787</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.153</t>
+          <t>7240447862.13735</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.154</t>
+          <t>7850163477.50212</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>8339571211.77466</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>8370486794.4117</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.156</t>
+          <t>9029265497.27929</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>11305888775.875</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.214</t>
+          <t>11982454910.5013</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.221</t>
+          <t>11950172231.4038</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.234</t>
+          <t>12020407133.5651</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.268</t>
+          <t>11723266445.9478</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.304</t>
+          <t>10711640614.5716</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.292</t>
+          <t>10304669793.8791</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.857</t>
+          <t>889082467.808174</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.844</t>
+          <t>1087224849.57736</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.759</t>
+          <t>975815913.147406</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.779</t>
+          <t>1003375515.39571</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.783</t>
+          <t>1104380713.23953</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.716</t>
+          <t>760943854.482319</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.718</t>
+          <t>1153497215.07183</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.774</t>
+          <t>1566227469.89919</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.959</t>
+          <t>1364973723.57595</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>1.117</t>
+          <t>1692833065.47887</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>1.179</t>
+          <t>1420164851.42786</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>1.273</t>
+          <t>1425350161.78628</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>1.477</t>
+          <t>1571625444.51721</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>1.692</t>
+          <t>1639841930.62404</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>1.619</t>
+          <t>1827139782.01815</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.566</t>
+          <t>1450.05146860667</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.551</t>
+          <t>1445.11229905404</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.507</t>
+          <t>1452.13089250117</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.523</t>
+          <t>1447.21352030129</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.523</t>
+          <t>1450.20095865434</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.493</t>
+          <t>1462.27211157893</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.497</t>
+          <t>1457.74140869849</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.526</t>
+          <t>1450.50582251384</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.637</t>
+          <t>1448.4262435801</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.745</t>
+          <t>1449.13485890453</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.783</t>
+          <t>1443.55946291955</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.849</t>
+          <t>1445.70502431118</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.979</t>
+          <t>1449.34600256235</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>1.103</t>
+          <t>1444.51931433683</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.973</t>
+          <t>1421.72699311897</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.256</t>
+          <t>1431.83445398875</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.247</t>
+          <t>1427.30241765905</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.223</t>
+          <t>1435.31652946537</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.229</t>
+          <t>1431.12211118966</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.226</t>
+          <t>1436.9631477049</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.207</t>
+          <t>1450.87893093097</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.208</t>
+          <t>1447.73669810223</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.227</t>
+          <t>1440.48394949547</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.279</t>
+          <t>1440.40678671357</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.322</t>
+          <t>1442.709962166</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.336</t>
+          <t>1437.94722395865</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.356</t>
+          <t>1441.14296810564</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.409</t>
+          <t>1446.10456800564</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.454</t>
+          <t>1441.1207861979</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.423</t>
+          <t>1418.14772449651</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-39.51</t>
+          <t>177513.724249902</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>-40.63</t>
+          <t>173479.376536638</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>-37.37</t>
+          <t>164690.676764728</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-36.66</t>
+          <t>162774.108847925</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-42.24</t>
+          <t>160458.565785168</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-43.25</t>
+          <t>161850.185048457</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-46.44</t>
+          <t>162421.29888976</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-50.02</t>
+          <t>170547.540206467</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>-56.48</t>
+          <t>200681.067021766</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-61.33</t>
+          <t>238705.533185001</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>-60.79</t>
+          <t>247065.800135292</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>-60.39</t>
+          <t>273343.026589669</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>-58.13</t>
+          <t>324688.835284459</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>-52.64</t>
+          <t>375094.150818069</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>-55.2</t>
+          <t>301037.714775515</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-4.21</t>
+          <t>4644433999.23136</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>-6.66</t>
+          <t>4406308436.57047</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>4361880946.91354</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>4260967080.51901</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-9.58</t>
+          <t>4229983283.49524</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-12.45</t>
+          <t>4691410356.24632</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-17.6</t>
+          <t>4569513186.92796</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-23.88</t>
+          <t>4434510774.34888</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>-35.98</t>
+          <t>4871537218.76409</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-40.64</t>
+          <t>5265999420.53189</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>-39.37</t>
+          <t>5217106451.73978</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>-38.31</t>
+          <t>5707252030.77318</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>-35.82</t>
+          <t>6151551960.40694</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>-28.8</t>
+          <t>7542075355.86073</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>-32.9</t>
+          <t>5189318812.10078</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>155354.044170616</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>152499.637195941</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>6.82</t>
+          <t>143810.096571035</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>144436.832500273</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>141951.659026442</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>147219.957489576</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-9.01</t>
+          <t>146747.689357156</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-16.5</t>
+          <t>148688.660044613</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>-40.17</t>
+          <t>175032.757146186</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-34.41</t>
+          <t>210429.495545863</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>-32.82</t>
+          <t>221153.776608734</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>-31.64</t>
+          <t>246146.915333527</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>-25.27</t>
+          <t>292889.792187384</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>-18.07</t>
+          <t>354991.525157902</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>-22.97</t>
+          <t>275136.130911899</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>5537.162</t>
+          <t>10456930536.0597</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>5534.511</t>
+          <t>10421001227.5703</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>5603.697</t>
+          <t>9981824391.77549</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>5685.502</t>
+          <t>10151121139.4538</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>5787.52</t>
+          <t>10753211697.3608</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>5961.599</t>
+          <t>11845829968.0076</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>6030.447</t>
+          <t>11896850510.1276</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>5990.895</t>
+          <t>12000480876.5456</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>5992.714</t>
+          <t>14165181810.2429</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>6057.565</t>
+          <t>15517157813.9813</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>6122.792</t>
+          <t>15681359578.7434</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>6209.157</t>
+          <t>16363297037.4329</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>6331.202</t>
+          <t>16559506832.1608</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>6412.834</t>
+          <t>18250505636.5095</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>6293.109</t>
+          <t>14989681936.3435</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>4595.1</t>
+          <t>22159.6800792858</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>4585.6</t>
+          <t>20979.7393406965</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>4644.6</t>
+          <t>20880.5801936927</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>4729.2</t>
+          <t>18337.2763476516</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>4818.4</t>
+          <t>18506.9067587257</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>4982.1</t>
+          <t>14630.227558881</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>5057.8</t>
+          <t>15673.6095326039</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>5033.1</t>
+          <t>21858.880161855</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>5028.4</t>
+          <t>25648.3098755797</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>5082.2</t>
+          <t>28276.0376391382</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>5144</t>
+          <t>25912.0235265583</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>5218.2</t>
+          <t>27196.1112561413</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>5322.6</t>
+          <t>31799.0430970755</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>5400.1</t>
+          <t>20102.6256601672</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>5284.4</t>
+          <t>25901.5838636155</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>9561.278</t>
+          <t>-5812496536.82833</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>8967.786</t>
+          <t>-6014692790.99985</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>8615.054</t>
+          <t>-5619943444.86195</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>8743.943</t>
+          <t>-5890154058.93481</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>8817.831</t>
+          <t>-6523228413.86556</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>9589.28</t>
+          <t>-7154419611.76124</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>9527.632</t>
+          <t>-7327337323.19964</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>9222.237</t>
+          <t>-7565970102.19674</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>9906.251</t>
+          <t>-9293644591.47886</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>10449.898</t>
+          <t>-10251158393.4494</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>10002.168</t>
+          <t>-10464253127.0036</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>10811.617</t>
+          <t>-10656045006.6597</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>11385.209</t>
+          <t>-10407954871.7538</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>13566.541</t>
+          <t>-10708430280.6487</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>10051.414</t>
+          <t>-9800363124.2427</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.082</t>
+          <t>117847.10491</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>112987.65254</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>102377.91139</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>103401.21995</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>100904.07742</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>91991.6699</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>90815.81233</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>97443.41446</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>118505.86321</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>135255.33413</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>137671.1065</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>145710.11847</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.152</t>
+          <t>166173.53261</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.198</t>
+          <t>183373.46257</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>168451.19134</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2644.885</t>
+          <t>0.0978464700979907</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2611.457</t>
+          <t>0.0949080462078143</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2622.384</t>
+          <t>0.0963275987408206</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2640.058</t>
+          <t>0.0971556147206706</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2665.412</t>
+          <t>0.0927849466609973</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2723.422</t>
+          <t>0.0953442867203299</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2734.402</t>
+          <t>0.0914933294647992</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2682.234</t>
+          <t>0.0918384345058358</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2664.038</t>
+          <t>0.0932349618221969</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2663.951</t>
+          <t>0.0966060783408884</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2638.288</t>
+          <t>0.0970105727587321</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2665.495</t>
+          <t>0.0956786815329086</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>2695.838</t>
+          <t>0.0951842776088228</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2711.455</t>
+          <t>0.0881891330282048</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2653.904</t>
+          <t>0.0812262665182415</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>145787.436978897</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>141086.82183962</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>127201.43659137</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>129745.94339465</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>130798.806343329</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>118625.892780869</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>121459.216405026</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>133173.760639047</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>162243.029399309</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>183289.402962845</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>189538.754053939</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>200242.206394935</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>229984.011665091</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>260066.435398422</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>249276.082989467</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>5041.832</t>
+          <t>172438.053732568</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>5171.235</t>
+          <t>166925.935825279</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>5001.634</t>
+          <t>150238.850509246</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>5066.976</t>
+          <t>152780.082432811</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>5667.328</t>
+          <t>153789.385768597</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>6013.843</t>
+          <t>139092.734411134</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>6499.238</t>
+          <t>142257.524134406</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>7009.9</t>
+          <t>155622.068038809</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>8610.635</t>
+          <t>189850.98373018</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>9149.006</t>
+          <t>214418.395190387</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>9088.578</t>
+          <t>221372.722061265</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>9100.422</t>
+          <t>233856.294647683</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>8808.876</t>
+          <t>268463.02295684</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>8153.071</t>
+          <t>304290.862609071</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>8502.035</t>
+          <t>291661.720887746</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>-8.86</t>
+          <t>856723.160922217</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-11.32</t>
+          <t>843663.633211832</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>-7.14</t>
+          <t>758561.906929261</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-6.67</t>
+          <t>779376.667471995</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-14.98</t>
+          <t>783058.218019589</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-17.16</t>
+          <t>715560.663943996</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>-22.18</t>
+          <t>718025.400210937</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>-28.2</t>
+          <t>774142.33641661</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>-41.6</t>
+          <t>959426.798719664</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-44.45</t>
+          <t>1117434.49111651</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>-43.4</t>
+          <t>1178579.94687948</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>-42.66</t>
+          <t>1273352.67021226</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>-39.58</t>
+          <t>1476781.63982967</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>-33.77</t>
+          <t>1691948.83062529</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>-37.85</t>
+          <t>1618600.58645843</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>0.689</t>
+          <t>172438.053732568</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>174972.110251644</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0.727</t>
+          <t>180485.867200163</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>0.725</t>
+          <t>183477.087066379</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>192019.397675357</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>197541.591392764</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.815</t>
+          <t>204298.36309091</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.767</t>
+          <t>205733.840799611</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>0.687</t>
+          <t>203974.716814737</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0.629</t>
+          <t>204434.566816834</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>0.597</t>
+          <t>206651.714656127</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>0.572</t>
+          <t>211469.592023376</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>0.518</t>
+          <t>218010.089434338</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>0.528</t>
+          <t>225203.004860929</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>0.486</t>
+          <t>222432.517407521</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>145787.436978897</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>148108.679842194</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>153161.249872419</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>156268.66213584</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>164173.134836257</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>169757.696272514</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>176199.126719409</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>177163.450461632</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>175487.571196141</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>176234.781917319</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>177815.765467754</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>181904.498785449</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>187670.198415123</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>193154.220820428</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>190343.137159385</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>83827.3371474317</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>80070.467084721</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>73070.4469907535</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>75720.8192271894</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>72656.0149914032</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>68224.621108866</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>65694.5345055935</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>71096.0202611915</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>89452.1209498204</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>107950.963989613</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>114334.715688735</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>121832.704612317</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>140566.39357316</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>149211.500500929</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>131472.882622254</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>4595100000</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>4585600000</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>4644600000</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>4729200000</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>4818400000</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>4982100000</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>5057800000</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>5033100000</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>5028400000</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>5082200000</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>5.144e+09</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>5218200000</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>5322600000</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>5400100000</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>5284400000</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>5537161563.7762</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>5534510709.31955</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>5603696769.77835</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>5685501816.20563</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>5787519958.512</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>5961599139.40131</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>6030447322.11266</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>5990894959.81838</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>5992714488.46031</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>6057565469.25483</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>6122792221.14095</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>6209157272.36833</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>6331201978.02203</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>6412833763.09854</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>6293109306.44956</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2644884976.88788</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2611456538.74614</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>2622383522.29246</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2640057926.02361</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2665411630.59851</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>2723422052.15245</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2734401947.43295</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>2682234091.96582</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>2664037662.86156</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>2663950545.87004</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>2638288062.32277</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>2665494682.89325</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>2695837875.11875</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>2711455230.61422</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>2653904109.09152</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>3867180</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>3877602</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>3904154</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>3972758</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>4027605</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>4108957</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>4165431</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>4158946</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>4160432</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>4198741</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>4258009</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>4308495</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>4378108</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>4449893.32227832</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>4437555.55062773</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>3168922</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>3173179</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>3198472</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>3267797</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>3322574</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>3407095</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>3469614</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>3469893</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>3471630</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>3507058</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>3563414</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>3609450</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>3672415</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>3738337</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>3716888</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>5537161563.7762</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>5534510709.31955</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>5603696769.77835</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>5685501816.20563</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>5787519958.512</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>5961599139.40131</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>6030447322.11266</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>5990894959.81838</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>5992714488.46031</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>6057565469.25483</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>6122792221.14095</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>6209157272.36833</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>6331201978.02203</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>6412833763.09854</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>6293109306.44956</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>4595100000</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>4585600000</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>4644600000</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>4729200000</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>4818400000</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>4982100000</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>5057800000</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>5033100000</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>5028400000</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>5082200000</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>5.144e+09</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>5218200000</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>5322600000</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>5400100000</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>5284400000</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.165843288808873</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.16971428572366</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.172865910570744</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.175109402495878</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.177047456686726</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.178402507200353</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.179995020415257</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.180132552108903</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.166563098005101</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.191720799927915</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.195351821530963</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.198012537488662</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.203713298460781</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.223534403901085</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.225223664202211</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.445526173294926</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.457877195974051</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.467406095339612</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.475852796445434</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.480561974817937</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.49979139344762</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.511218651781974</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.519639347364957</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.502523407533596</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.545194857547996</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.554528964233844</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.561598394579096</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.573414145424168</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.564980568882856</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.569376291647569</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.388630537896201</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.372408518302289</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.359727994089643</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.349037801058688</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.342390568495337</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.321806099352027</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.308786327802769</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.30022810052614</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.330913494461304</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.263084342524089</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.250119214235193</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.240389067932242</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.222872556115051</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.21148502721606</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.20540004415022</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.115659741544566</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.119230744064524</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.122177648215674</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.124250611989703</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.125694294726123</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.127273408489188</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.129670759247346</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.13126738276117</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.132653441270207</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.139381275156615</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.141954420237789</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.142477529378672</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.148554207443421</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.170539732797016</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.172267612866357</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.458345020135554</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.472067124700069</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.482795676750388</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.492247004959802</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.499927097718679</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.517127740576561</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.529645758851097</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.538480827969708</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.54663524183637</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.567256667411875</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.578512912924773</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.587281382681211</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.593824328538605</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.587424750347006</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.592746490029178</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.42599523831988</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.408702131235407</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.395026675033938</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.383502383050495</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.374378607555198</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.355598850934251</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.340683481901557</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.330251789269123</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.320711316893423</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.29336205743151</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.279532666837438</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.270241087940117</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.257621464017973</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.242035516855977</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.234985897104465</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>565662.49026</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>551434.48693</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>507003.8431</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>522685.70802</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>523220.59463</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>492505.09565</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>496622.57662</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>526176.36293</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>637060.47889</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>745492.87068</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>783492.97772</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>848835.80683</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>978761.05105</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>1103399.79032</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>972907.41524</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>256265.39088</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>246996.40291</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>223309.2975</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>228500.90166</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>226445.40076</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>207317.35552</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>207952.05864</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>226718.0883</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>279303.10468</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>322369.35918</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>335707.43775</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>355688.99926</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>409029.41653</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>453502.36311</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>423134.60351</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>625363.65605692</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>642240.787117299</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>660940.924905751</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>680429.847094052</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>700182.100497513</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>721449.55282383</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>742284.419267126</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>759731.713392547</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>776340.031278286</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>796201.566599279</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>818671.25242229</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>841202.487809592</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>866528.736035931</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>892642.539159863</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>914298.655567405</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>zdW13</t>
